--- a/clase/checklist-gobdata.xlsx
+++ b/clase/checklist-gobdata.xlsx
@@ -622,7 +622,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Se cuenta con un Oficial de Protección de Datos (DPO).</t>
+          <t>Se designó una persona o área responsable de atender consultas y reclamos de los titulares (Ley 1581).</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
